--- a/uploads/papers/None/config.xlsx
+++ b/uploads/papers/None/config.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\python\testsystem题库\2025信息技术（8套）\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\python\testsystem题库\试卷\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23203" windowHeight="9985"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="21736" windowHeight="8355"/>
   </bookViews>
   <sheets>
     <sheet name="答题卡配置" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="26">
   <si>
     <t>题号</t>
   </si>
@@ -43,51 +43,75 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>c</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>b</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>填空</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>3空</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>d</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>c</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>b</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>b</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>d</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>d</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>a</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>for、i、print</t>
+  </si>
+  <si>
+    <t>填空题规则：不同空用"、"隔开（全角顿号），同一空多个答案用"|"分隔，如"in|IN、i、1|一"表示第1空填in或IN都正确</t>
+  </si>
+  <si>
+    <t>备注</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>A</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>B</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>C</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>C</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>C</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>C</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>B</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>B</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>D</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>A</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>B</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,3,5,7,9</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>2|二</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>数据输出</t>
+  </si>
+  <si>
+    <t>信息</t>
+  </si>
+  <si>
+    <t>简答</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -95,7 +119,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -116,6 +140,14 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -125,7 +157,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -148,15 +180,30 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -459,14 +506,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:F32"/>
   <sheetFormatPr defaultRowHeight="12.9" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="3" max="3" width="12" customWidth="1"/>
     <col min="5" max="5" width="18.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -482,8 +529,11 @@
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="F1" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A2">
         <v>1</v>
       </c>
@@ -497,10 +547,10 @@
         <v>4</v>
       </c>
       <c r="E2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.15">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A3">
         <v>2</v>
       </c>
@@ -514,10 +564,10 @@
         <v>4</v>
       </c>
       <c r="E3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.15">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A4">
         <v>3</v>
       </c>
@@ -531,10 +581,10 @@
         <v>4</v>
       </c>
       <c r="E4" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.15">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A5">
         <v>4</v>
       </c>
@@ -548,10 +598,10 @@
         <v>4</v>
       </c>
       <c r="E5" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.15">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A6">
         <v>5</v>
       </c>
@@ -565,10 +615,10 @@
         <v>4</v>
       </c>
       <c r="E6" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.15">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A7">
         <v>6</v>
       </c>
@@ -582,10 +632,10 @@
         <v>4</v>
       </c>
       <c r="E7" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.15">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A8">
         <v>7</v>
       </c>
@@ -599,10 +649,10 @@
         <v>4</v>
       </c>
       <c r="E8" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.15">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A9">
         <v>8</v>
       </c>
@@ -616,10 +666,10 @@
         <v>4</v>
       </c>
       <c r="E9" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.15">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A10">
         <v>9</v>
       </c>
@@ -633,10 +683,10 @@
         <v>4</v>
       </c>
       <c r="E10" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.15">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A11">
         <v>10</v>
       </c>
@@ -650,10 +700,10 @@
         <v>4</v>
       </c>
       <c r="E11" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A12">
         <v>11</v>
       </c>
@@ -667,10 +717,10 @@
         <v>4</v>
       </c>
       <c r="E12" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.15">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A13">
         <v>12</v>
       </c>
@@ -684,10 +734,10 @@
         <v>4</v>
       </c>
       <c r="E13" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.15">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A14">
         <v>13</v>
       </c>
@@ -704,7 +754,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A15">
         <v>14</v>
       </c>
@@ -718,10 +768,10 @@
         <v>4</v>
       </c>
       <c r="E15" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A16">
         <v>15</v>
       </c>
@@ -735,10 +785,10 @@
         <v>4</v>
       </c>
       <c r="E16" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.15">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A17">
         <v>16</v>
       </c>
@@ -752,10 +802,10 @@
         <v>4</v>
       </c>
       <c r="E17" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.15">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A18">
         <v>17</v>
       </c>
@@ -769,10 +819,10 @@
         <v>4</v>
       </c>
       <c r="E18" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A19">
         <v>18</v>
       </c>
@@ -786,10 +836,10 @@
         <v>4</v>
       </c>
       <c r="E19" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.15">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A20">
         <v>19</v>
       </c>
@@ -803,10 +853,10 @@
         <v>4</v>
       </c>
       <c r="E20" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.15">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A21">
         <v>20</v>
       </c>
@@ -820,10 +870,10 @@
         <v>4</v>
       </c>
       <c r="E21" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.15">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A22">
         <v>21</v>
       </c>
@@ -837,10 +887,10 @@
         <v>4</v>
       </c>
       <c r="E22" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.15">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A23">
         <v>22</v>
       </c>
@@ -854,10 +904,10 @@
         <v>4</v>
       </c>
       <c r="E23" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.15">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A24">
         <v>23</v>
       </c>
@@ -871,10 +921,10 @@
         <v>4</v>
       </c>
       <c r="E24" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.15">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A25">
         <v>24</v>
       </c>
@@ -888,10 +938,10 @@
         <v>4</v>
       </c>
       <c r="E25" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.15">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A26">
         <v>25</v>
       </c>
@@ -905,27 +955,81 @@
         <v>4</v>
       </c>
       <c r="E26" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.15">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A27">
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>9</v>
-      </c>
-      <c r="C27" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D27">
-        <v>3</v>
-      </c>
-      <c r="E27" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" ht="10.199999999999999" customHeight="1" x14ac:dyDescent="0.15"/>
+        <v>5</v>
+      </c>
+      <c r="E27">
+        <v>8</v>
+      </c>
+      <c r="F27" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A28">
+        <v>27</v>
+      </c>
+      <c r="B28" t="s">
+        <v>7</v>
+      </c>
+      <c r="D28">
+        <v>5</v>
+      </c>
+      <c r="E28" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A29">
+        <v>28</v>
+      </c>
+      <c r="B29" t="s">
+        <v>7</v>
+      </c>
+      <c r="E29" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" ht="16.3" x14ac:dyDescent="0.25">
+      <c r="A30">
+        <v>29</v>
+      </c>
+      <c r="B30" t="s">
+        <v>7</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" ht="16.3" x14ac:dyDescent="0.25">
+      <c r="A31">
+        <v>30</v>
+      </c>
+      <c r="B31" t="s">
+        <v>7</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A32">
+        <v>31</v>
+      </c>
+      <c r="B32" t="s">
+        <v>25</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
